--- a/314e-ig/output/StructureDefinition-attachment-inlineDataSavedAsFile.xlsx
+++ b/314e-ig/output/StructureDefinition-attachment-inlineDataSavedAsFile.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T11:15:06+05:30</t>
+    <t>2026-05-13T15:29:14+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
